--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moonlabpc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D5525D-9D17-4F3D-B66D-410876558762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329419BA-48E6-4795-BC72-27D7E4DC06B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moonlabpc\Documents\PAGINA WEB\NUMKO_web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bede5c5a56f12ed6/Documentos/PAGINA WEB/NUMKO_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51A08C69-05E3-4BA0-BC67-E4D33D9B68A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D27D2CC1-5355-43CC-9015-F23A002910E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
